--- a/app1/Excelfiles/August2023.xlsx
+++ b/app1/Excelfiles/August2023.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29.43357142857143" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
@@ -1524,13 +1524,68 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="F53" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>test VAue</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>05-03-2025</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>taj mahal</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Kitchen Holds</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="F55" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="F56" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="F57" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
